--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -32817,12 +32817,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -32832,12 +32832,12 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="I16" s="22" t="n">
-        <v>12457237</v>
+        <v>48653588</v>
       </c>
       <c r="J16" s="26" t="inlineStr">
         <is>
@@ -32854,23 +32854,21 @@
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.8164227183294704</v>
+        <v>0.8081594299047473</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>0.58659774</v>
+        <v>0.7269213</v>
       </c>
       <c r="N16" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O16" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O16" s="24" t="n">
+        <v>2.5319312</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -32879,12 +32877,12 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -32894,12 +32892,12 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -32908,7 +32906,7 @@
         </is>
       </c>
       <c r="I17" s="22" t="n">
-        <v>48653588</v>
+        <v>12457237</v>
       </c>
       <c r="J17" s="26" t="inlineStr">
         <is>
@@ -32916,21 +32914,23 @@
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.8081594299047473</v>
+        <v>0.8068747010339026</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.7269213</v>
+        <v>0.58659774</v>
       </c>
       <c r="N17" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O17" s="24" t="n">
-        <v>2.5319312</v>
+      <c r="O17" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -32976,10 +32976,10 @@
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.8062111750244484</v>
+        <v>0.802895071145605</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.828</v>
+        <v>0.803</v>
       </c>
       <c r="M18" s="24" t="n">
         <v>0.2320380985386871</v>
@@ -51801,10 +51801,10 @@
         </is>
       </c>
       <c r="K7" s="24" t="n">
-        <v>0.7483747819327972</v>
+        <v>0.7397178222661022</v>
       </c>
       <c r="L7" s="24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="M7" s="27" t="inlineStr">
         <is>
@@ -65023,10 +65023,10 @@
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.6223828899889503</v>
+        <v>0.619711718787281</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="M11" s="24" t="n">
         <v>0.9437919</v>
@@ -65259,10 +65259,10 @@
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.578025607501778</v>
+        <v>0.5742798753931376</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.739</v>
+        <v>0.701</v>
       </c>
       <c r="M15" s="24" t="n">
         <v>0.33102494</v>
@@ -65553,10 +65553,10 @@
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.555827069716932</v>
+        <v>0.5520472864940897</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.588</v>
+        <v>0.55</v>
       </c>
       <c r="M20" s="24" t="n">
         <v>0.7176173</v>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -52122,36 +52122,36 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>SKAND.OL</t>
+          <t>PRIC-B.ST</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Skandia GreenPower AS</t>
+          <t>Pricer AB (publ)</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>Independent Power and Renewable Electricity Producers</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I13" s="22" t="n">
-        <v>19848335.28486846</v>
+        <v>68830954.20963286</v>
       </c>
       <c r="J13" s="26" t="inlineStr">
         <is>
@@ -52159,19 +52159,21 @@
         </is>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.5611153957437102</v>
+        <v>0.5636755923274757</v>
       </c>
       <c r="L13" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="24" t="n">
-        <v>1.8742586</v>
-      </c>
-      <c r="N13" s="25" t="n">
-        <v>3.94</v>
+        <v>0.58504397</v>
+      </c>
+      <c r="N13" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O13" s="24" t="n">
-        <v>0.2493113</v>
+        <v>0.30395496</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -52180,27 +52182,27 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>CEMAT.CO</t>
+          <t>SKAND.OL</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Cemat A/S</t>
+          <t>Skandia GreenPower AS</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Independent Power and Renewable Electricity Producers</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -52209,29 +52211,27 @@
         </is>
       </c>
       <c r="I14" s="22" t="n">
-        <v>33402859.47088336</v>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>19848335.28486846</v>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.5566654665206502</v>
+        <v>0.5611153957437102</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.9039666</v>
-      </c>
-      <c r="N14" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.8742586</v>
+      </c>
+      <c r="N14" s="25" t="n">
+        <v>3.94</v>
       </c>
       <c r="O14" s="24" t="n">
-        <v>1.1935964</v>
+        <v>0.2493113</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -52240,27 +52240,27 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>GGEO.ST</t>
+          <t>CEMAT.CO</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Guideline Geo AB (publ)</t>
+          <t>Cemat A/S</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>Energy Equipment &amp; Services</t>
+          <t>Real Estate Management &amp; Development</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -52269,21 +52269,21 @@
         </is>
       </c>
       <c r="I15" s="22" t="n">
-        <v>10613705.88981759</v>
-      </c>
-      <c r="J15" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>33402859.47088336</v>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.5558207726676844</v>
+        <v>0.5566654665206502</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.625</v>
+        <v>0.989</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>0.7455325</v>
+        <v>0.9039666</v>
       </c>
       <c r="N15" s="27" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>0.47706202</v>
+        <v>1.1935964</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -52300,12 +52300,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>PRIC-B.ST</t>
+          <t>GGEO.ST</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Pricer AB (publ)</t>
+          <t>Guideline Geo AB (publ)</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -52315,21 +52315,21 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Energy Equipment &amp; Services</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="I16" s="22" t="n">
-        <v>68830954.20963286</v>
+        <v>10613705.88981759</v>
       </c>
       <c r="J16" s="26" t="inlineStr">
         <is>
@@ -52337,13 +52337,13 @@
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.5544350088466974</v>
+        <v>0.5558207726676844</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>0.58504397</v>
+        <v>0.7455325</v>
       </c>
       <c r="N16" s="27" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         </is>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.30395496</v>
+        <v>0.47706202</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -59139,36 +59139,34 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>GEST.MC</t>
+          <t>ELSTR.AT</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Gestamp Automocion S.A.</t>
+          <t>Elastron S.A. - Steel Service Centers</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>Auto Components</t>
-        </is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="n">
+        <v/>
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I22" s="22" t="n">
-        <v>1939274358.011536</v>
+        <v>54860998.78386497</v>
       </c>
       <c r="J22" s="26" t="inlineStr">
         <is>
@@ -59176,19 +59174,19 @@
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.4601482867945089</v>
+        <v>0.4659925273728007</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.989</v>
+        <v>0.778</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>0.7032365</v>
+        <v>0.5548496000000001</v>
       </c>
       <c r="N22" s="25" t="n">
-        <v>2.8499998</v>
+        <v>3.95</v>
       </c>
       <c r="O22" s="24" t="n">
-        <v>0.1474581</v>
+        <v>0.28365088</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -59197,34 +59195,36 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>ELSTR.AT</t>
+          <t>GEST.MC</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Elastron S.A. - Steel Service Centers</t>
+          <t>Gestamp Automocion S.A.</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v/>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>Auto Components</t>
+        </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="I23" s="22" t="n">
-        <v>54860998.78386497</v>
+        <v>1939274358.011536</v>
       </c>
       <c r="J23" s="26" t="inlineStr">
         <is>
@@ -59232,19 +59232,19 @@
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.4595375877517608</v>
+        <v>0.4601482867945089</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.778</v>
+        <v>0.989</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>0.5548496000000001</v>
+        <v>0.7032365</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>3.95</v>
+        <v>2.8499998</v>
       </c>
       <c r="O23" s="24" t="n">
-        <v>0.28365088</v>
+        <v>0.1474581</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -73,15 +73,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52_3954_T" sheetId="64" state="visible" r:id="rId64"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="53_ELC_V" sheetId="65" state="visible" r:id="rId65"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="54_5951_T" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="55_5MZ_SI" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="56_200570_SZ" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="57_010240_KQ" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="58_1758_T" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="59_CAAS" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="60_1795_T" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="61_7446_T" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="62_BEC_BK" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="63_HMVL_NS" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="55_200570_SZ" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="56_010240_KQ" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="57_1758_T" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="58_CAAS" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="59_1795_T" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="60_7446_T" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="61_BEC_BK" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="62_HMVL_NS" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="63_5MZ_SI" sheetId="75" state="visible" r:id="rId75"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64_051390_KQ" sheetId="76" state="visible" r:id="rId76"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="65_11C_SG" sheetId="77" state="visible" r:id="rId77"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="66_8119_T" sheetId="78" state="visible" r:id="rId78"/>
@@ -24266,17 +24266,17 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>5MZ.SI</t>
+          <t>200570.SZ</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
         <is>
-          <t>Kingsmen Creatives Ltd.</t>
+          <t>Changchai Company, Limited</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="G58" s="20" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="H58" s="21" t="inlineStr">
@@ -24295,27 +24295,27 @@
         </is>
       </c>
       <c r="I58" s="22" t="n">
-        <v>83349515.04073143</v>
-      </c>
-      <c r="J58" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>185502384.3848075</v>
+      </c>
+      <c r="J58" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K58" s="24" t="n">
-        <v>0.9975771617508232</v>
+        <v>0.9971632762149122</v>
       </c>
       <c r="L58" s="24" t="n">
-        <v>0.828</v>
+        <v>0.965</v>
       </c>
       <c r="M58" s="24" t="n">
-        <v>0.8656959</v>
+        <v>0.35128185</v>
       </c>
       <c r="N58" s="25" t="n">
-        <v>5.609999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="O58" s="24" t="n">
-        <v>0.28319883</v>
+        <v>0.4855134910686547</v>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
@@ -24324,17 +24324,17 @@
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>200570.SZ</t>
+          <t>010240.KQ</t>
         </is>
       </c>
       <c r="D59" s="18" t="inlineStr">
         <is>
-          <t>Changchai Company, Limited</t>
+          <t>Heungkuk Metaltech Co.,Ltd.</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -24342,18 +24342,16 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G59" s="20" t="inlineStr">
-        <is>
-          <t>Machinery</t>
-        </is>
+      <c r="G59" s="20" t="n">
+        <v/>
       </c>
       <c r="H59" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="I59" s="22" t="n">
-        <v>185502384.3848075</v>
+        <v>39287311.76283239</v>
       </c>
       <c r="J59" s="26" t="inlineStr">
         <is>
@@ -24361,19 +24359,21 @@
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>0.9971632762149122</v>
+        <v>0.995064554128435</v>
       </c>
       <c r="L59" s="24" t="n">
-        <v>0.965</v>
+        <v>1</v>
       </c>
       <c r="M59" s="24" t="n">
-        <v>0.35128185</v>
-      </c>
-      <c r="N59" s="25" t="n">
-        <v>1.35</v>
+        <v>0.4945990275563788</v>
+      </c>
+      <c r="N59" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O59" s="24" t="n">
-        <v>0.4855134910686547</v>
+        <v>0.4255336271917211</v>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
@@ -24382,17 +24382,17 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>010240.KQ</t>
+          <t>1758.T</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
         <is>
-          <t>Heungkuk Metaltech Co.,Ltd.</t>
+          <t>Taiyo Kisokogyo Co.,Ltd.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F60" s="20" t="inlineStr">
@@ -24400,8 +24400,10 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G60" s="20" t="n">
-        <v/>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>Construction &amp; Engineering</t>
+        </is>
       </c>
       <c r="H60" s="21" t="inlineStr">
         <is>
@@ -24409,29 +24411,27 @@
         </is>
       </c>
       <c r="I60" s="22" t="n">
-        <v>39287311.76283239</v>
-      </c>
-      <c r="J60" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>29562048.10560452</v>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>0.995064554128435</v>
+        <v>0.9949179353364078</v>
       </c>
       <c r="L60" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M60" s="24" t="n">
-        <v>0.4945990275563788</v>
-      </c>
-      <c r="N60" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.49718443</v>
+      </c>
+      <c r="N60" s="25" t="n">
+        <v>2.71</v>
       </c>
       <c r="O60" s="24" t="n">
-        <v>0.4255336271917211</v>
+        <v>0.33027256</v>
       </c>
     </row>
     <row r="61" ht="17" customHeight="1">
@@ -24440,56 +24440,58 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>1758.T</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="D61" s="18" t="inlineStr">
         <is>
-          <t>Taiyo Kisokogyo Co.,Ltd.</t>
+          <t>China Automotive Systems, Inc.</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G61" s="20" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="H61" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I61" s="22" t="n">
-        <v>29562048.10560452</v>
-      </c>
-      <c r="J61" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>159301312</v>
+      </c>
+      <c r="J61" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>0.9949179353364078</v>
+        <v>0.9920988152517629</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M61" s="24" t="n">
-        <v>0.49718443</v>
-      </c>
-      <c r="N61" s="25" t="n">
-        <v>2.71</v>
+        <v>0.35896394</v>
+      </c>
+      <c r="N61" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O61" s="24" t="n">
-        <v>0.33027256</v>
+        <v>0.19081154</v>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
@@ -24498,58 +24500,56 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>1795.T</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
         <is>
-          <t>China Automotive Systems, Inc.</t>
+          <t>Masaru Corporation</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G62" s="20" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
       <c r="H62" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="I62" s="22" t="n">
-        <v>159301312</v>
-      </c>
-      <c r="J62" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>31737190.16144858</v>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="K62" s="24" t="n">
-        <v>0.9920988152517629</v>
+        <v>0.9895432520182381</v>
       </c>
       <c r="L62" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M62" s="24" t="n">
-        <v>0.35896394</v>
-      </c>
-      <c r="N62" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.95958775</v>
+      </c>
+      <c r="N62" s="25" t="n">
+        <v>2.24</v>
       </c>
       <c r="O62" s="24" t="n">
-        <v>0.19081154</v>
+        <v>0.5153487</v>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
@@ -24558,12 +24558,12 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>1795.T</t>
+          <t>7446.T</t>
         </is>
       </c>
       <c r="D63" s="18" t="inlineStr">
         <is>
-          <t>Masaru Corporation</t>
+          <t>Tohoku Chemical Co., Ltd.</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -24573,12 +24573,12 @@
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G63" s="20" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="H63" s="21" t="inlineStr">
@@ -24587,27 +24587,27 @@
         </is>
       </c>
       <c r="I63" s="22" t="n">
-        <v>31737190.16144858</v>
-      </c>
-      <c r="J63" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>25387340.54314424</v>
+      </c>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K63" s="24" t="n">
-        <v>0.9895432520182381</v>
+        <v>0.9895172733395478</v>
       </c>
       <c r="L63" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M63" s="24" t="n">
-        <v>0.95958775</v>
+        <v>0.46368754</v>
       </c>
       <c r="N63" s="25" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="O63" s="24" t="n">
-        <v>0.5153487</v>
+        <v>0.114462115</v>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
@@ -24616,36 +24616,36 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>7446.T</t>
+          <t>BEC.BK</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>Tohoku Chemical Co., Ltd.</t>
+          <t>BEC World Public Company Limited</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G64" s="20" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H64" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I64" s="22" t="n">
-        <v>25387340.54314424</v>
+        <v>117253956.7947385</v>
       </c>
       <c r="J64" s="26" t="inlineStr">
         <is>
@@ -24653,19 +24653,19 @@
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>0.9895172733395478</v>
+        <v>0.987347177946116</v>
       </c>
       <c r="L64" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M64" s="24" t="n">
-        <v>0.46368754</v>
+        <v>0.6399203999999999</v>
       </c>
       <c r="N64" s="25" t="n">
-        <v>2.27</v>
+        <v>4.8499998</v>
       </c>
       <c r="O64" s="24" t="n">
-        <v>0.114462115</v>
+        <v>1.0508382</v>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
@@ -24674,17 +24674,17 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>BEC.BK</t>
+          <t>HMVL.NS</t>
         </is>
       </c>
       <c r="D65" s="18" t="inlineStr">
         <is>
-          <t>BEC World Public Company Limited</t>
+          <t>Hindustan Media Ventures Limited</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="G65" s="20" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Diversified Telecommunication Services</t>
         </is>
       </c>
       <c r="H65" s="21" t="inlineStr">
@@ -24703,7 +24703,7 @@
         </is>
       </c>
       <c r="I65" s="22" t="n">
-        <v>117253956.7947385</v>
+        <v>61515955.22155485</v>
       </c>
       <c r="J65" s="26" t="inlineStr">
         <is>
@@ -24711,19 +24711,21 @@
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>0.987347177946116</v>
+        <v>0.9873140581974352</v>
       </c>
       <c r="L65" s="24" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
       <c r="M65" s="24" t="n">
-        <v>0.6399203999999999</v>
-      </c>
-      <c r="N65" s="25" t="n">
-        <v>4.8499998</v>
+        <v>0.3708259</v>
+      </c>
+      <c r="N65" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O65" s="24" t="n">
-        <v>1.0508382</v>
+        <v>0.76226425</v>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
@@ -24732,27 +24734,27 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>HMVL.NS</t>
+          <t>5MZ.SI</t>
         </is>
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>Hindustan Media Ventures Limited</t>
+          <t>Kingsmen Creatives Ltd.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G66" s="20" t="inlineStr">
         <is>
-          <t>Diversified Telecommunication Services</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="H66" s="21" t="inlineStr">
@@ -24761,29 +24763,27 @@
         </is>
       </c>
       <c r="I66" s="22" t="n">
-        <v>61515955.22155485</v>
-      </c>
-      <c r="J66" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>83349515.04073143</v>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>0.9873140581974352</v>
+        <v>0.9838723751423676</v>
       </c>
       <c r="L66" s="24" t="n">
-        <v>0.805</v>
+        <v>0.828</v>
       </c>
       <c r="M66" s="24" t="n">
-        <v>0.3708259</v>
-      </c>
-      <c r="N66" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8656959</v>
+      </c>
+      <c r="N66" s="25" t="n">
+        <v>5.609999999999999</v>
       </c>
       <c r="O66" s="24" t="n">
-        <v>0.76226425</v>
+        <v>0.28319883</v>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
@@ -49975,7 +49975,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#55    5MZ.SI    Kingsmen Creatives Ltd.</t>
+          <t>#55    200570.SZ    Changchai Company, Limited</t>
         </is>
       </c>
     </row>
@@ -49993,9 +49993,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -50004,7 +50004,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.9975771617508232</v>
+        <v>0.9971632762149122</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -50022,7 +50022,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
@@ -50046,7 +50046,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Machinery</t>
         </is>
       </c>
     </row>
@@ -50069,7 +50069,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>83349515.04073143</v>
+        <v>185502384.3848075</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -50079,7 +50079,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>289359062.3855591</v>
+        <v>382074623.6659699</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -50090,7 +50090,7 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -50104,7 +50104,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Kingsmen Creatives - founder Benedict Soh; FY24 rev +7%/earn +360%; experiential/attractions growth</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -50125,7 +50125,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.5731900445033157</v>
+        <v>0.5572301068538207</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.5515608674607254</v>
+        <v>0.8566904686594516</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -50143,7 +50143,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.4271108752530269</v>
+        <v>0.4403531013595818</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         </is>
       </c>
       <c r="E22" s="24" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -50161,7 +50161,7 @@
         </is>
       </c>
       <c r="C23" s="24" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.7051282051282051</v>
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.710759</v>
+        <v>0.747682</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.2156</v>
+        <v>1.193</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -50197,7 +50197,7 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.5211183150865403</v>
+        <v>0.4044505010629498</v>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -50222,7 +50222,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.8656959</v>
+        <v>0.35128185</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>61.27200589781432</v>
+        <v>143.8250528549478</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -50240,7 +50240,7 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>2.915</v>
+        <v>-4.807063888047561</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -50248,7 +50248,7 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-3.275786955964635</v>
+        <v>-14.66162258187258</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -50258,7 +50258,7 @@
         </is>
       </c>
       <c r="C30" s="24" t="n">
-        <v>12.77851533020667</v>
+        <v>0.3422699735771106</v>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -50266,7 +50266,7 @@
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>33.86105492453711</v>
+        <v>8.6143813045774</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -50276,7 +50276,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>7.6428576</v>
+        <v>15.22009968815923</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         </is>
       </c>
       <c r="E31" s="25" t="n">
-        <v>6.2846267823398</v>
+        <v>6.18452300213143</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -50294,7 +50294,7 @@
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>0.28319883</v>
+        <v>0.4855134910686547</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>61.707</v>
+        <v>1.0679999</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -50312,7 +50312,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>2.23556183032855</v>
+        <v>20.07137064026483</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>67.08232001968177</v>
+        <v>139.1939526805084</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>3.05932472993346</v>
+        <v>20.73960569163904</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -50350,7 +50350,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>2.89503715544789</v>
+        <v>25.06106634731536</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -50358,7 +50358,7 @@
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>9.26</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -50378,14 +50378,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.87)</t>
+          <t>·  Sub-book  (P/B 0.35)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (62% insider)</t>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -50399,7 +50399,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.8x); cash 81% of mcap; cash &gt; EV (2.90x, net cash 67% mcap)</t>
+          <t>growth-flip; first-positive: FCF/CFO; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.3x); cash 105% of mcap; cash &gt; EV (25.06x, net cash 102% mcap)</t>
         </is>
       </c>
     </row>
@@ -50450,495 +50450,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>#56    200570.SZ    Changchai Company, Limited</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="29" t="n"/>
-      <c r="B2" s="29" t="n"/>
-      <c r="C2" s="29" t="n"/>
-      <c r="D2" s="29" t="n"/>
-      <c r="E2" s="29" t="n"/>
-      <c r="F2" s="29" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="n">
-        <v>0.9971632762149122</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>Machinery</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="n">
-        <v>185502384.3848075</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="n">
-        <v>382074623.6659699</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="36" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="n">
-        <v>0.5572301068538207</v>
-      </c>
-      <c r="D21" s="36" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>0.8566904686594516</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="36" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>0.4403531013595818</v>
-      </c>
-      <c r="D22" s="36" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>0.7051282051282051</v>
-      </c>
-      <c r="D23" s="36" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="36" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="n">
-        <v>0.747682</v>
-      </c>
-      <c r="D24" s="36" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="n">
-        <v>1.193</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="n">
-        <v>0.4044505010629498</v>
-      </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>0.35128185</v>
-      </c>
-      <c r="D28" s="36" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>143.8250528549478</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>-4.807063888047561</v>
-      </c>
-      <c r="D29" s="36" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="n">
-        <v>-14.66162258187258</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="36" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>0.3422699735771106</v>
-      </c>
-      <c r="D30" s="36" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>8.6143813045774</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="36" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>15.22009968815923</v>
-      </c>
-      <c r="D31" s="36" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>6.18452300213143</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="36" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0.4855134910686547</v>
-      </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>1.0679999</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="n">
-        <v>20.07137064026483</v>
-      </c>
-      <c r="D33" s="36" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="25" t="n">
-        <v>139.1939526805084</v>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>20.73960569163904</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="36" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>25.06106634731536</v>
-      </c>
-      <c r="D35" s="36" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>14.41</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="37" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.35)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="38" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: FCF/CFO; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.3x); cash 105% of mcap; cash &gt; EV (25.06x, net cash 102% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="39" t="n"/>
-      <c r="B48" s="39" t="n"/>
-      <c r="C48" s="39" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="39" t="n"/>
-      <c r="F48" s="39" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 56 of 100</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -50953,7 +50464,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#57    010240.KQ    Heungkuk Metaltech Co.,Ltd.</t>
+          <t>#56    010240.KQ    Heungkuk Metaltech Co.,Ltd.</t>
         </is>
       </c>
     </row>
@@ -51391,7 +50902,7 @@
     <row r="48">
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 57 of 100</t>
+          <t>Asymmetry Workbook  ·  Sheet 56 of 100</t>
         </is>
       </c>
     </row>
@@ -51413,6 +50924,503 @@
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="B42:E44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#57    1758.T    Taiyo Kisokogyo Co.,Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="29" t="n"/>
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="29" t="n"/>
+      <c r="D2" s="29" t="n"/>
+      <c r="E2" s="29" t="n"/>
+      <c r="F2" s="29" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>0.9949179353364078</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Construction &amp; Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Nano Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>29562048.10560452</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n">
+        <v>90471184.00543889</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Taiyo Kisokogyo - cash&gt;EV + 3% yield BUT no announced TSE reform plan; construction cyclicality</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>0.6502731603505933</v>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>0.8329135521415676</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>0.5497117379940532</v>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>0.740906</v>
+      </c>
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>0.4892123529151101</v>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>0.49718443</v>
+      </c>
+      <c r="D28" s="36" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>101.7206815442373</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>-4.147582161869242</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>4.334641167697845</v>
+      </c>
+      <c r="D30" s="36" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>11.108952215822</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>10.209356</v>
+      </c>
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>6.485413487576181</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0.33027256</v>
+      </c>
+      <c r="D32" s="36" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>46.447</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>10.43148572823971</v>
+      </c>
+      <c r="D33" s="36" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>77.45014604718921</v>
+      </c>
+      <c r="D34" s="36" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>7.63524398318748</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>3.59053258983853</v>
+      </c>
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (46% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="38" t="inlineStr">
+        <is>
+          <t>growth-flip; first-positive: FCF; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.8x); cash 80% of mcap; cash &gt; EV (3.59x, net cash 77% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="46" ht="18" customHeight="1"/>
+    <row r="49">
+      <c r="A49" s="39" t="n"/>
+      <c r="B49" s="39" t="n"/>
+      <c r="C49" s="39" t="n"/>
+      <c r="D49" s="39" t="n"/>
+      <c r="E49" s="39" t="n"/>
+      <c r="F49" s="39" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 57 of 100</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B44:E46"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53045,6 +53053,477 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#58    CAAS    China Automotive Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="29" t="n"/>
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="29" t="n"/>
+      <c r="D2" s="29" t="n"/>
+      <c r="E2" s="29" t="n"/>
+      <c r="F2" s="29" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>0.9920988152517629</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>159301312</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n">
+        <v>765736000</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>0.5601669980674424</v>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>0.6123668253251274</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>0.5155073222606764</v>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>0.6086956521739132</v>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>0.7110674193484872</v>
+      </c>
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>0.6177871059013622</v>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>0.35896394</v>
+      </c>
+      <c r="D28" s="36" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>117.9530386236229</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>2.777771335984681</v>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>-0.8935041979673001</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>2.890987168635948</v>
+      </c>
+      <c r="D30" s="36" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>15.74238506042344</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>2.7789476</v>
+      </c>
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>8.865979919972409</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0.19081154</v>
+      </c>
+      <c r="D32" s="36" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>64.765</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>45.69247556520861</v>
+      </c>
+      <c r="D33" s="36" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>45.2828768914895</v>
+      </c>
+      <c r="D34" s="36" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>17.63632313518247</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>1.536442869830014</v>
+      </c>
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>26.46</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (65% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="n"/>
+      <c r="B42" s="39" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 58 of 100</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -53059,7 +53538,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#58    1758.T    Taiyo Kisokogyo Co.,Ltd.</t>
+          <t>#59    1795.T    Masaru Corporation</t>
         </is>
       </c>
     </row>
@@ -53077,9 +53556,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -53088,7 +53567,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.9949179353364078</v>
+        <v>0.9895432520182381</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -53153,7 +53632,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>29562048.10560452</v>
+        <v>31737190.16144858</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -53163,7 +53642,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>90471184.00543889</v>
+        <v>66382512.30691764</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -53174,7 +53653,7 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -53188,7 +53667,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Taiyo Kisokogyo - cash&gt;EV + 3% yield BUT no announced TSE reform plan; construction cyclicality</t>
+          <t>Masaru Corporation - building renewal niche (aging Japan stock tailwind), 42% insider, real div, cash&gt;EV</t>
         </is>
       </c>
     </row>
@@ -53209,7 +53688,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.6502731603505933</v>
+        <v>0.656546060570587</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -53217,7 +53696,7 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.8329135521415676</v>
+        <v>0.4010643787180105</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -53227,7 +53706,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.5497117379940532</v>
+        <v>0.5603685485459839</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -53235,7 +53714,7 @@
         </is>
       </c>
       <c r="E22" s="24" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -53253,7 +53732,7 @@
         </is>
       </c>
       <c r="E23" s="24" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -53263,7 +53742,7 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.740906</v>
+        <v>0.790203</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -53281,7 +53760,7 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.4892123529151101</v>
+        <v>0.5156010784568359</v>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
@@ -53289,7 +53768,7 @@
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -53306,7 +53785,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.49718443</v>
+        <v>0.95958775</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -53314,7 +53793,7 @@
         </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>101.7206815442373</v>
+        <v>76.94572034965516</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -53324,7 +53803,7 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>1.72</v>
+        <v>3.071</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -53332,7 +53811,7 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-4.147582161869242</v>
+        <v>-2.73129691152947</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -53341,8 +53820,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n">
-        <v>4.334641167697845</v>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -53350,7 +53831,7 @@
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>11.108952215822</v>
+        <v>18.32037364830446</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -53360,7 +53841,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>10.209356</v>
+        <v>12.274353</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
@@ -53368,7 +53849,7 @@
         </is>
       </c>
       <c r="E31" s="25" t="n">
-        <v>6.485413487576181</v>
+        <v>7.022030789967661</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -53378,7 +53859,7 @@
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>0.33027256</v>
+        <v>0.5153487</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -53386,7 +53867,7 @@
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>46.447</v>
+        <v>41.059</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -53396,7 +53877,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>10.43148572823971</v>
+        <v>28.30422949850665</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -53416,7 +53897,7 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>77.45014604718921</v>
+        <v>47.54225430188343</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -53424,7 +53905,7 @@
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>7.63524398318748</v>
+        <v>19.00031673248309</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -53434,7 +53915,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>3.59053258983853</v>
+        <v>1.32222491698681</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -53442,7 +53923,7 @@
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>16.9</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -53462,21 +53943,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.50)</t>
+          <t>·  Sub-book  (P/B 0.96)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (46% insider)</t>
+          <t>·  Insider-aligned  (41% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -53490,7 +53971,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: FCF; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.8x); cash 80% of mcap; cash &gt; EV (3.59x, net cash 77% mcap)</t>
+          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 3.6x); cash 70% of mcap; cash &gt; EV (1.32x, net cash 48% mcap)</t>
         </is>
       </c>
     </row>
@@ -53507,7 +53988,7 @@
     <row r="50">
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 58 of 100</t>
+          <t>Asymmetry Workbook  ·  Sheet 59 of 100</t>
         </is>
       </c>
     </row>
@@ -53528,477 +54009,6 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B44:E46"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>#59    CAAS    China Automotive Systems, Inc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="29" t="n"/>
-      <c r="B2" s="29" t="n"/>
-      <c r="C2" s="29" t="n"/>
-      <c r="D2" s="29" t="n"/>
-      <c r="E2" s="29" t="n"/>
-      <c r="F2" s="29" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="n">
-        <v>0.9920988152517629</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>Auto Components</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="n">
-        <v>159301312</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="n">
-        <v>765736000</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="36" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="n">
-        <v>0.5601669980674424</v>
-      </c>
-      <c r="D21" s="36" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>0.6123668253251274</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="36" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>0.5155073222606764</v>
-      </c>
-      <c r="D22" s="36" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>0.6086956521739132</v>
-      </c>
-      <c r="D23" s="36" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="36" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="n">
-        <v>0.7110674193484872</v>
-      </c>
-      <c r="D24" s="36" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="n">
-        <v>0.6177871059013622</v>
-      </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>0.35896394</v>
-      </c>
-      <c r="D28" s="36" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>117.9530386236229</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>2.777771335984681</v>
-      </c>
-      <c r="D29" s="36" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="n">
-        <v>-0.8935041979673001</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="36" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>2.890987168635948</v>
-      </c>
-      <c r="D30" s="36" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>15.74238506042344</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="36" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>2.7789476</v>
-      </c>
-      <c r="D31" s="36" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>8.865979919972409</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="36" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0.19081154</v>
-      </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>64.765</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="n">
-        <v>45.69247556520861</v>
-      </c>
-      <c r="D33" s="36" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="25" t="n">
-        <v>45.2828768914895</v>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>17.63632313518247</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="36" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>1.536442869830014</v>
-      </c>
-      <c r="D35" s="36" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>26.46</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.36)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="37" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (65% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="39" t="n"/>
-      <c r="B42" s="39" t="n"/>
-      <c r="C42" s="39" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="39" t="n"/>
-      <c r="F42" s="39" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 59 of 100</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -54027,7 +54037,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#60    1795.T    Masaru Corporation</t>
+          <t>#60    7446.T    Tohoku Chemical Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -54045,9 +54055,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -54056,7 +54066,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.9895432520182381</v>
+        <v>0.9895172733395478</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -54086,7 +54096,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
     </row>
@@ -54098,7 +54108,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -54121,7 +54131,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>31737190.16144858</v>
+        <v>25387340.54314424</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -54131,7 +54141,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>66382512.30691764</v>
+        <v>214730912.7778853</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -54156,7 +54166,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Masaru Corporation - building renewal niche (aging Japan stock tailwind), 42% insider, real div, cash&gt;EV</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -54177,7 +54187,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.656546060570587</v>
+        <v>0.5790758214520549</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -54185,7 +54195,7 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.4010643787180105</v>
+        <v>0.5990069195384256</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -54195,7 +54205,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.5603685485459839</v>
+        <v>0.5231129389049806</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -54203,7 +54213,7 @@
         </is>
       </c>
       <c r="E22" s="24" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -54213,7 +54223,7 @@
         </is>
       </c>
       <c r="C23" s="24" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
@@ -54221,7 +54231,7 @@
         </is>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -54231,7 +54241,7 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.790203</v>
+        <v>0.560161</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -54239,7 +54249,7 @@
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.2</v>
+        <v>1.2667</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -54249,7 +54259,7 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.5156010784568359</v>
+        <v>0.5659160572822478</v>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
@@ -54257,7 +54267,7 @@
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -54274,7 +54284,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.95958775</v>
+        <v>0.46368754</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -54282,7 +54292,7 @@
         </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>76.94572034965516</v>
+        <v>62.81258704452841</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -54292,7 +54302,7 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>3.071</v>
+        <v>0.856</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -54300,7 +54310,7 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-2.73129691152947</v>
+        <v>-3.590141114713602</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -54309,10 +54319,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="24" t="n">
+        <v>1.148034626192238</v>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -54320,7 +54328,7 @@
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>18.32037364830446</v>
+        <v>11.63112127187149</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -54330,7 +54338,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>12.274353</v>
+        <v>7.3260074</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
@@ -54338,7 +54346,7 @@
         </is>
       </c>
       <c r="E31" s="25" t="n">
-        <v>7.022030789967661</v>
+        <v>2.35064836086099</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -54348,7 +54356,7 @@
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>0.5153487</v>
+        <v>0.114462115</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -54356,7 +54364,7 @@
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>41.059</v>
+        <v>32.072</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -54366,7 +54374,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>28.30422949850665</v>
+        <v>56.6832008997868</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -54386,7 +54394,7 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>47.54225430188343</v>
+        <v>70.06245716807565</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -54394,7 +54402,7 @@
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>19.00031673248309</v>
+        <v>7.112116069337179</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -54404,7 +54412,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>1.32222491698681</v>
+        <v>2.646721454259635</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -54412,7 +54420,7 @@
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>32.25</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -54432,21 +54440,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.96)</t>
+          <t>·  Sub-book  (P/B 0.46)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (41% insider)</t>
+          <t>·  Insider-aligned  (32% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -54460,7 +54468,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 3.6x); cash 70% of mcap; cash &gt; EV (1.32x, net cash 48% mcap)</t>
+          <t>growth-flip; first-positive: FCF/CFO; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.2x); cash 92% of mcap; cash &gt; EV (2.65x, net cash 70% mcap)</t>
         </is>
       </c>
     </row>
@@ -54512,7 +54520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -54526,7 +54534,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#61    7446.T    Tohoku Chemical Co., Ltd.</t>
+          <t>#61    BEC.BK    BEC World Public Company Limited</t>
         </is>
       </c>
     </row>
@@ -54555,7 +54563,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.9895172733395478</v>
+        <v>0.987347177946116</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -54573,7 +54581,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
@@ -54585,7 +54593,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
     </row>
@@ -54597,7 +54605,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -54609,7 +54617,7 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -54620,7 +54628,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>25387340.54314424</v>
+        <v>117253956.7947385</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -54630,7 +54638,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>214730912.7778853</v>
+        <v>116193391.140706</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -54676,7 +54684,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.5790758214520549</v>
+        <v>0.5485262099700645</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -54684,7 +54692,7 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.5990069195384256</v>
+        <v>0.7613187320627166</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -54694,7 +54702,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.5231129389049806</v>
+        <v>0.3911453039313603</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -54712,7 +54720,7 @@
         </is>
       </c>
       <c r="C23" s="24" t="n">
-        <v>0.641025641025641</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
@@ -54730,7 +54738,7 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.560161</v>
+        <v>0.915171</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -54738,7 +54746,7 @@
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.2667</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -54748,7 +54756,7 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.5659160572822478</v>
+        <v>0.2724419445836099</v>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
@@ -54756,7 +54764,7 @@
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -54773,7 +54781,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.46368754</v>
+        <v>0.6399203999999999</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -54781,7 +54789,7 @@
         </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>62.81258704452841</v>
+        <v>84.22801075268818</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -54791,7 +54799,7 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>0.856</v>
+        <v>1.278</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -54799,7 +54807,7 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-3.590141114713602</v>
+        <v>-12.0819078498878</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -54809,7 +54817,7 @@
         </is>
       </c>
       <c r="C30" s="24" t="n">
-        <v>1.148034626192238</v>
+        <v>12.65647969559208</v>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -54817,7 +54825,7 @@
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>11.63112127187149</v>
+        <v>12.82305445334267</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -54827,7 +54835,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>7.3260074</v>
+        <v>24.125</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
@@ -54835,7 +54843,7 @@
         </is>
       </c>
       <c r="E31" s="25" t="n">
-        <v>2.35064836086099</v>
+        <v>7.522678297532449</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -54845,7 +54853,7 @@
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>0.114462115</v>
+        <v>1.0508382</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -54853,7 +54861,7 @@
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>32.072</v>
+        <v>78.905</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -54863,7 +54871,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>56.6832008997868</v>
+        <v>29.84741698924731</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -54883,7 +54891,7 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>70.06245716807565</v>
+        <v>93.4558064516129</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -54891,7 +54899,7 @@
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>7.112116069337179</v>
+        <v>-10.02889608462793</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -54901,7 +54909,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>2.646721454259635</v>
+        <v>18.77484506314048</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -54909,7 +54917,7 @@
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>19.71</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -54929,72 +54937,64 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.46)</t>
+          <t>·  Sub-book  (P/B 0.64)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (32% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="37" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+          <t>·  Insider-aligned  (79% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="38" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: FCF/CFO; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.2x); cash 92% of mcap; cash &gt; EV (2.65x, net cash 70% mcap)</t>
-        </is>
-      </c>
-    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="38" t="inlineStr">
+        <is>
+          <t>under-priced vs fundamentals; cheap+grow (EV/EBIT 0.7x); cash 123% of mcap; cash &gt; EV (18.77x, net cash 93% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
     <row r="45" ht="18" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="39" t="n"/>
+      <c r="B48" s="39" t="n"/>
+      <c r="C48" s="39" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="39" t="n"/>
+      <c r="F48" s="39" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" s="39" t="n"/>
-      <c r="B49" s="39" t="n"/>
-      <c r="C49" s="39" t="n"/>
-      <c r="D49" s="39" t="n"/>
-      <c r="E49" s="39" t="n"/>
-      <c r="F49" s="39" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 61 of 100</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -55023,7 +55023,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#62    BEC.BK    BEC World Public Company Limited</t>
+          <t>#62    HMVL.NS    Hindustan Media Ventures Limited</t>
         </is>
       </c>
     </row>
@@ -55052,7 +55052,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.987347177946116</v>
+        <v>0.9873140581974352</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -55070,7 +55070,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -55094,7 +55094,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Diversified Telecommunication Services</t>
         </is>
       </c>
     </row>
@@ -55117,7 +55117,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>117253956.7947385</v>
+        <v>61515955.22155485</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -55127,7 +55127,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>116193391.140706</v>
+        <v>77957286.68756734</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -55138,7 +55138,7 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -55173,7 +55173,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.5485262099700645</v>
+        <v>0.5669331370642752</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.7613187320627166</v>
+        <v>0.8162673186352319</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -55191,7 +55191,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.3911453039313603</v>
+        <v>0.4178371364720024</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.915171</v>
+        <v>0.761605</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.2</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -55245,7 +55245,7 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.2724419445836099</v>
+        <v>0.4474513106014685</v>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -55270,7 +55270,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.6399203999999999</v>
+        <v>0.3708259</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>84.22801075268818</v>
+        <v>80.36889380697623</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -55288,7 +55288,7 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>1.278</v>
+        <v>-2.336</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-12.0819078498878</v>
+        <v>-6.691705063541612</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -55305,8 +55305,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n">
-        <v>12.65647969559208</v>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -55314,7 +55316,7 @@
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>12.82305445334267</v>
+        <v>13.33079479368596</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -55324,7 +55326,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>24.125</v>
+        <v>3.4499137</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
@@ -55332,7 +55334,7 @@
         </is>
       </c>
       <c r="E31" s="25" t="n">
-        <v>7.522678297532449</v>
+        <v>17.8464664057054</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -55342,7 +55344,7 @@
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>1.0508382</v>
+        <v>0.76226425</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -55350,7 +55352,7 @@
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>78.905</v>
+        <v>86.38500000000001</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -55360,7 +55362,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>29.84741698924731</v>
+        <v>5.40649792705699</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -55380,7 +55382,7 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>93.4558064516129</v>
+        <v>153.5320443207245</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -55388,7 +55390,7 @@
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>-10.02889608462793</v>
+        <v>10.06580694661669</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -55398,7 +55400,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>18.77484506314048</v>
+        <v>2.062596146950393</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -55406,7 +55408,7 @@
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>4.27</v>
+        <v>8.959999999999999</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -55426,14 +55428,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.64)</t>
+          <t>·  Sub-book  (P/B 0.37)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (79% insider)</t>
+          <t>·  Insider-aligned  (86% insider)</t>
         </is>
       </c>
     </row>
@@ -55447,7 +55449,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>under-priced vs fundamentals; cheap+grow (EV/EBIT 0.7x); cash 123% of mcap; cash &gt; EV (18.77x, net cash 93% mcap)</t>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 6.7x); cash 226% of mcap; cash &gt; EV (2.06x, net cash 209% mcap)</t>
         </is>
       </c>
     </row>
@@ -55512,7 +55514,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>#63    HMVL.NS    Hindustan Media Ventures Limited</t>
+          <t>#63    5MZ.SI    Kingsmen Creatives Ltd.</t>
         </is>
       </c>
     </row>
@@ -55530,9 +55532,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="40" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -55541,7 +55543,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.9873140581974352</v>
+        <v>0.9838723751423676</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -55559,7 +55561,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
@@ -55571,7 +55573,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -55583,7 +55585,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Diversified Telecommunication Services</t>
+          <t>Professional Services</t>
         </is>
       </c>
     </row>
@@ -55606,7 +55608,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>61515955.22155485</v>
+        <v>83349515.04073143</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -55616,7 +55618,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>77957286.68756734</v>
+        <v>289359062.3855591</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -55627,7 +55629,7 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -55641,7 +55643,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Kingsmen Creatives - founder Benedict Soh; FY24 rev +7%/earn +360%; experiential/attractions growth</t>
         </is>
       </c>
     </row>
@@ -55662,7 +55664,7 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.5669331370642752</v>
+        <v>0.5731900445033157</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -55670,7 +55672,7 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.8162673186352319</v>
+        <v>0.5515608674607254</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -55680,7 +55682,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.4178371364720024</v>
+        <v>0.4271108752530269</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -55688,7 +55690,7 @@
         </is>
       </c>
       <c r="E22" s="24" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -55716,7 +55718,7 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.761605</v>
+        <v>0.710759</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -55724,7 +55726,7 @@
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.161</v>
+        <v>1.1989</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -55734,7 +55736,7 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.4474513106014685</v>
+        <v>0.5211183150865403</v>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
@@ -55759,7 +55761,7 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.3708259</v>
+        <v>0.8656959</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -55767,7 +55769,7 @@
         </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>80.36889380697623</v>
+        <v>61.27200589781432</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -55777,7 +55779,7 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>-2.336</v>
+        <v>2.915</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -55785,7 +55787,7 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-6.691705063541612</v>
+        <v>-3.275786955964635</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -55794,10 +55796,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="24" t="n">
+        <v>12.77851533020667</v>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         </is>
       </c>
       <c r="E30" s="25" t="n">
-        <v>13.33079479368596</v>
+        <v>33.86105492453711</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -55815,7 +55815,7 @@
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>3.4499137</v>
+        <v>7.6428576</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
@@ -55823,7 +55823,7 @@
         </is>
       </c>
       <c r="E31" s="25" t="n">
-        <v>17.8464664057054</v>
+        <v>6.2846267823398</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -55833,7 +55833,7 @@
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>0.76226425</v>
+        <v>0.28319883</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         </is>
       </c>
       <c r="E32" s="25" t="n">
-        <v>86.38500000000001</v>
+        <v>61.707</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -55851,7 +55851,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>5.40649792705699</v>
+        <v>2.23556183032855</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>153.5320443207245</v>
+        <v>67.08232001968177</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         </is>
       </c>
       <c r="E34" s="25" t="n">
-        <v>10.06580694661669</v>
+        <v>3.05932472993346</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -55889,7 +55889,7 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>2.062596146950393</v>
+        <v>2.89503715544789</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>8.959999999999999</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -55917,14 +55917,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.37)</t>
+          <t>·  Sub-book  (P/B 0.87)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (86% insider)</t>
+          <t>·  Insider-aligned  (62% insider)</t>
         </is>
       </c>
     </row>
@@ -55938,7 +55938,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 6.7x); cash 226% of mcap; cash &gt; EV (2.06x, net cash 209% mcap)</t>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.8x); cash 81% of mcap; cash &gt; EV (2.90x, net cash 67% mcap)</t>
         </is>
       </c>
     </row>
@@ -64713,7 +64713,7 @@
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.9293896188023903</v>
+        <v>0.9228340533769973</v>
       </c>
       <c r="L6" s="24" t="n">
         <v>0.717</v>
@@ -64773,7 +64773,7 @@
         </is>
       </c>
       <c r="K7" s="24" t="n">
-        <v>0.9139679418013134</v>
+        <v>0.8953155348257763</v>
       </c>
       <c r="L7" s="24" t="n">
         <v>0.625</v>
@@ -64856,56 +64856,56 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>KNR1L.VS</t>
+          <t>6P5.F</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>AB Kauno Energija</t>
+          <t>PlayWay S.A.</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Interactive Media &amp; Services</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="I9" s="22" t="n">
-        <v>104708685.6114807</v>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>404606041.3139191</v>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.6785944886246847</v>
+        <v>0.6796598917224573</v>
       </c>
       <c r="L9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.6397103</v>
+        <v>0.98127</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>1.17999995</v>
+        <v>7.59</v>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.7342359000000001</v>
+        <v>88.30949370090597</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -64914,56 +64914,56 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>6P5.F</t>
+          <t>KNR1L.VS</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>PlayWay S.A.</t>
+          <t>AB Kauno Energija</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Services</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I10" s="22" t="n">
-        <v>404606041.3139191</v>
-      </c>
-      <c r="J10" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>104708685.6114807</v>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.6714381994838792</v>
+        <v>0.6785944886246847</v>
       </c>
       <c r="L10" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0.98127</v>
+        <v>0.6397103</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>7.59</v>
+        <v>1.17999995</v>
       </c>
       <c r="O10" s="24" t="n">
-        <v>88.30949370090597</v>
+        <v>0.7342359000000001</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -65067,7 +65067,7 @@
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.6036149764029989</v>
+        <v>0.6112146277762111</v>
       </c>
       <c r="L12" s="24" t="n">
         <v>0.832</v>
@@ -65187,7 +65187,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.5841182380434016</v>
+        <v>0.5920277284961096</v>
       </c>
       <c r="L14" s="24" t="n">
         <v>1</v>
@@ -65208,56 +65208,58 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>6PJ.F</t>
+          <t>PKG1T.TL</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>TOYA S.A.</t>
+          <t>AS Pro Kapital Grupp</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Real Estate Management &amp; Development</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="I15" s="22" t="n">
-        <v>204187664.152359</v>
-      </c>
-      <c r="J15" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>42192163.846138</v>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.5742798753931376</v>
+        <v>0.5730199156885645</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.701</v>
+        <v>1</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>0.33102494</v>
-      </c>
-      <c r="N15" s="25" t="n">
-        <v>1.97</v>
+        <v>0.5494037000000001</v>
+      </c>
+      <c r="N15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>14.65695443958162</v>
+        <v>0.7207516</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -65266,58 +65268,56 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>PKG1T.TL</t>
+          <t>6PJ.F</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>AS Pro Kapital Grupp</t>
+          <t>TOYA S.A.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I16" s="22" t="n">
-        <v>42192163.846138</v>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>204187664.152359</v>
+      </c>
+      <c r="J16" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.5730199156885645</v>
+        <v>0.5718155779532427</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>1</v>
+        <v>0.701</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>0.5494037000000001</v>
-      </c>
-      <c r="N16" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.33102494</v>
+      </c>
+      <c r="N16" s="25" t="n">
+        <v>1.97</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.7207516</v>
+        <v>14.65695443958162</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -65562,12 +65562,12 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>7T8.F</t>
+          <t>ZAP.WA</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Asseco South Eastern Europe S.A.</t>
+          <t>Zaklady Azotowe Pulawy</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -65575,43 +65575,41 @@
           <t>PL</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
+      <c r="F21" s="20" t="n">
+        <v/>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v/>
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="I21" s="22" t="n">
-        <v>1032375865.560242</v>
-      </c>
-      <c r="J21" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>241823774.1585045</v>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.5444617714069632</v>
+        <v>0.5424820193209716</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>1</v>
+        <v>0.912</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.7763317</v>
-      </c>
-      <c r="N21" s="25" t="n">
-        <v>2.6099999</v>
+        <v>0.33582735</v>
+      </c>
+      <c r="N21" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O21" s="24" t="n">
-        <v>38.00760200389541</v>
+        <v>0.2259833</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -65620,12 +65618,12 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>ZAP.WA</t>
+          <t>7T8.F</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Zaklady Azotowe Pulawy</t>
+          <t>Asseco South Eastern Europe S.A.</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -65633,41 +65631,43 @@
           <t>PL</t>
         </is>
       </c>
-      <c r="F22" s="20" t="n">
-        <v/>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v/>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="I22" s="22" t="n">
-        <v>241823774.1585045</v>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>1032375865.560242</v>
+      </c>
+      <c r="J22" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.5424820193209716</v>
+        <v>0.5407975918053431</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.912</v>
+        <v>1</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>0.33582735</v>
-      </c>
-      <c r="N22" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.7763317</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>2.6099999</v>
       </c>
       <c r="O22" s="24" t="n">
-        <v>0.2259833</v>
+        <v>38.00760200389541</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
